--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marlen\PycharmProjects\edms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{89748A09-D0DF-4FBA-B33B-A38FC0C5E16E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE4E384B-A43F-4949-BD32-F75FBBA5BCE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B00D21D6-71DC-4FDB-9CB6-65DCE6EA6F08}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="26">
   <si>
     <t>Advance search button (search document by tag or text)</t>
   </si>
@@ -112,6 +112,12 @@
   </si>
   <si>
     <t>нужно обсудить</t>
+  </si>
+  <si>
+    <t>+</t>
+  </si>
+  <si>
+    <t>вручную на транмиттале</t>
   </si>
 </sst>
 </file>
@@ -488,7 +494,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{988267C0-7ACC-420D-BB4D-9DDC7B21EEE5}">
-  <dimension ref="I6:J25"/>
+  <dimension ref="H6:J25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="9" max="9" width="72.28515625" bestFit="1" customWidth="1"/>
@@ -580,7 +586,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H17" t="s">
+        <v>24</v>
+      </c>
       <c r="I17" t="s">
         <v>1</v>
       </c>
@@ -588,7 +597,10 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H18" t="s">
+        <v>24</v>
+      </c>
       <c r="I18" t="s">
         <v>2</v>
       </c>
@@ -596,7 +608,10 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H19" t="s">
+        <v>24</v>
+      </c>
       <c r="I19" t="s">
         <v>3</v>
       </c>
@@ -604,7 +619,10 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H20" t="s">
+        <v>24</v>
+      </c>
       <c r="I20" t="s">
         <v>4</v>
       </c>
@@ -612,27 +630,36 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="8:10" x14ac:dyDescent="0.25">
       <c r="I21" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H22" t="s">
+        <v>24</v>
+      </c>
       <c r="I22" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="23" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="J22" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="8:10" x14ac:dyDescent="0.25">
       <c r="I23" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="8:10" x14ac:dyDescent="0.25">
       <c r="I24" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="25" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H25" t="s">
+        <v>24</v>
+      </c>
       <c r="I25" t="s">
         <v>19</v>
       </c>

--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -2,18 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <workbookPr codeName="ЭтаКнига" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marlen\PycharmProjects\edms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE4E384B-A43F-4949-BD32-F75FBBA5BCE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E365290-C8B2-4E57-96E0-7E415C15C7CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B00D21D6-71DC-4FDB-9CB6-65DCE6EA6F08}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
+    <sheet name="Лист2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$I$6:$J$25</definedName>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="25">
   <si>
     <t>Advance search button (search document by tag or text)</t>
   </si>
@@ -115,9 +116,6 @@
   </si>
   <si>
     <t>+</t>
-  </si>
-  <si>
-    <t>вручную на транмиттале</t>
   </si>
 </sst>
 </file>
@@ -494,6 +492,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{988267C0-7ACC-420D-BB4D-9DDC7B21EEE5}">
+  <sheetPr codeName="Лист1"/>
   <dimension ref="H6:J25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -575,15 +574,18 @@
     </row>
     <row r="15" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I15" t="s">
-        <v>12</v>
-      </c>
-      <c r="J15" s="1" t="s">
-        <v>11</v>
+        <v>3</v>
+      </c>
+      <c r="J15" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="9:10" x14ac:dyDescent="0.25">
       <c r="I16" t="s">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="J16" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="8:10" x14ac:dyDescent="0.25">
@@ -591,10 +593,10 @@
         <v>24</v>
       </c>
       <c r="I17" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="J17" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="8:10" x14ac:dyDescent="0.25">
@@ -602,10 +604,10 @@
         <v>24</v>
       </c>
       <c r="I18" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="J18" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="8:10" x14ac:dyDescent="0.25">
@@ -613,10 +615,10 @@
         <v>24</v>
       </c>
       <c r="I19" t="s">
-        <v>3</v>
-      </c>
-      <c r="J19" t="s">
-        <v>23</v>
+        <v>12</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="8:10" x14ac:dyDescent="0.25">
@@ -624,7 +626,7 @@
         <v>24</v>
       </c>
       <c r="I20" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J20" t="s">
         <v>23</v>
@@ -632,7 +634,10 @@
     </row>
     <row r="21" spans="8:10" x14ac:dyDescent="0.25">
       <c r="I21" t="s">
-        <v>13</v>
+        <v>2</v>
+      </c>
+      <c r="J21" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="22" spans="8:10" x14ac:dyDescent="0.25">
@@ -640,20 +645,17 @@
         <v>24</v>
       </c>
       <c r="I22" t="s">
-        <v>15</v>
-      </c>
-      <c r="J22" t="s">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="8:10" x14ac:dyDescent="0.25">
       <c r="I23" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24" spans="8:10" x14ac:dyDescent="0.25">
       <c r="I24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25" spans="8:10" x14ac:dyDescent="0.25">
@@ -661,7 +663,7 @@
         <v>24</v>
       </c>
       <c r="I25" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -671,9 +673,18 @@
     </sortState>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="J15" r:id="rId1" xr:uid="{729B1202-1063-4B50-A459-E48A517DA70F}"/>
+    <hyperlink ref="J19" r:id="rId1" xr:uid="{729B1202-1063-4B50-A459-E48A517DA70F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7480AC4-18BB-4BAF-9356-F56D111A8A31}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -8,13 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marlen\PycharmProjects\edms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E365290-C8B2-4E57-96E0-7E415C15C7CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B1F8111-5CAA-48A0-9C0D-3E615B286C50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B00D21D6-71DC-4FDB-9CB6-65DCE6EA6F08}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
-    <sheet name="Лист2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$I$6:$J$25</definedName>
@@ -41,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="26">
   <si>
     <t>Advance search button (search document by tag or text)</t>
   </si>
@@ -116,6 +115,9 @@
   </si>
   <si>
     <t>+</t>
+  </si>
+  <si>
+    <t>Presentation</t>
   </si>
 </sst>
 </file>
@@ -493,7 +495,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{988267C0-7ACC-420D-BB4D-9DDC7B21EEE5}">
   <sheetPr codeName="Лист1"/>
-  <dimension ref="H6:J25"/>
+  <dimension ref="H6:J26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="9" max="9" width="72.28515625" bestFit="1" customWidth="1"/>
@@ -589,9 +591,6 @@
       </c>
     </row>
     <row r="17" spans="8:10" x14ac:dyDescent="0.25">
-      <c r="H17" t="s">
-        <v>24</v>
-      </c>
       <c r="I17" t="s">
         <v>15</v>
       </c>
@@ -600,9 +599,6 @@
       </c>
     </row>
     <row r="18" spans="8:10" x14ac:dyDescent="0.25">
-      <c r="H18" t="s">
-        <v>24</v>
-      </c>
       <c r="I18" t="s">
         <v>19</v>
       </c>
@@ -611,39 +607,30 @@
       </c>
     </row>
     <row r="19" spans="8:10" x14ac:dyDescent="0.25">
-      <c r="H19" t="s">
-        <v>24</v>
-      </c>
       <c r="I19" t="s">
+        <v>2</v>
+      </c>
+      <c r="J19" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="I20" t="s">
         <v>12</v>
       </c>
-      <c r="J19" s="1" t="s">
+      <c r="J20" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="20" spans="8:10" x14ac:dyDescent="0.25">
-      <c r="H20" t="s">
-        <v>24</v>
-      </c>
-      <c r="I20" t="s">
-        <v>1</v>
-      </c>
-      <c r="J20" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="21" spans="8:10" x14ac:dyDescent="0.25">
       <c r="I21" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J21" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="22" spans="8:10" x14ac:dyDescent="0.25">
-      <c r="H22" t="s">
-        <v>24</v>
-      </c>
       <c r="I22" t="s">
         <v>0</v>
       </c>
@@ -664,6 +651,14 @@
       </c>
       <c r="I25" t="s">
         <v>18</v>
+      </c>
+    </row>
+    <row r="26" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H26" t="s">
+        <v>24</v>
+      </c>
+      <c r="I26" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -673,18 +668,9 @@
     </sortState>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="J19" r:id="rId1" xr:uid="{729B1202-1063-4B50-A459-E48A517DA70F}"/>
+    <hyperlink ref="J20" r:id="rId1" xr:uid="{729B1202-1063-4B50-A459-E48A517DA70F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7480AC4-18BB-4BAF-9356-F56D111A8A31}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/tasks.xlsx
+++ b/tasks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marlen\PycharmProjects\edms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B1F8111-5CAA-48A0-9C0D-3E615B286C50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E45133F-AD86-4460-8E96-5B1771A227E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B00D21D6-71DC-4FDB-9CB6-65DCE6EA6F08}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="27">
   <si>
     <t>Advance search button (search document by tag or text)</t>
   </si>
@@ -118,6 +118,9 @@
   </si>
   <si>
     <t>Presentation</t>
+  </si>
+  <si>
+    <t>при отправке трансмиттала если файла нет, то ошибка</t>
   </si>
 </sst>
 </file>
@@ -495,7 +498,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{988267C0-7ACC-420D-BB4D-9DDC7B21EEE5}">
   <sheetPr codeName="Лист1"/>
-  <dimension ref="H6:J26"/>
+  <dimension ref="H6:J28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="9" max="9" width="72.28515625" bestFit="1" customWidth="1"/>
@@ -659,6 +662,11 @@
       </c>
       <c r="I26" t="s">
         <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="I28" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
